--- a/Libraries/Vehicle/Suspension/AxleTA2PR/sm_car_data_Linkage_AxleTA2PR.xlsx
+++ b/Libraries/Vehicle/Suspension/AxleTA2PR/sm_car_data_Linkage_AxleTA2PR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Suspension\AxleTA2PR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SMILLER\TMW\Sharepoint\PM_Evl\sscMbody\2024\2409_VDGUP\Models_and_Files\Proj1\CAD_251201_New\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED365363-59BB-4833-8C04-F81304753238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58AFF2DF-F8F5-471A-B616-63199762F47F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11235" tabRatio="794" xr2:uid="{5368FE27-1559-47FB-BDD2-777FB297959A}"/>
+    <workbookView xWindow="31050" yWindow="2250" windowWidth="21600" windowHeight="11295" tabRatio="794" xr2:uid="{5368FE27-1559-47FB-BDD2-777FB297959A}"/>
   </bookViews>
   <sheets>
     <sheet name="AxleTA2PR_SUV_Landy_f" sheetId="5" r:id="rId1"/>
@@ -716,7 +716,7 @@
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:S37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="17" customWidth="1"/>
@@ -730,7 +730,7 @@
     <col min="11" max="13" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -750,7 +750,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -764,7 +764,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>6</v>
       </c>
@@ -776,7 +776,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
@@ -791,7 +791,7 @@
       </c>
       <c r="J4" s="18"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>41</v>
       </c>
@@ -808,7 +808,7 @@
       </c>
       <c r="J5" s="18"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="8"/>
       <c r="B6" s="9" t="s">
         <v>40</v>
@@ -823,16 +823,25 @@
         <v>26</v>
       </c>
       <c r="F6" s="10">
+        <v>-0.84</v>
+      </c>
+      <c r="G6" s="10">
+        <v>0.439</v>
+      </c>
+      <c r="H6" s="10">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="K6" s="10">
         <v>-0.81950000000000001</v>
       </c>
-      <c r="G6" s="10">
+      <c r="L6" s="10">
         <v>0.438</v>
       </c>
-      <c r="H6" s="10">
+      <c r="M6" s="10">
         <v>0.39500000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="8"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9" t="s">
@@ -848,13 +857,22 @@
         <v>0</v>
       </c>
       <c r="G7" s="10">
+        <v>0.438</v>
+      </c>
+      <c r="H7" s="10">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="K7" s="10">
+        <v>0</v>
+      </c>
+      <c r="L7" s="10">
         <v>0.4405</v>
       </c>
-      <c r="H7" s="10">
+      <c r="M7" s="10">
         <v>0.38</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9" t="s">
@@ -866,10 +884,10 @@
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
       <c r="H8" s="10">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
       <c r="B9" s="9" t="s">
         <v>25</v>
@@ -884,16 +902,25 @@
         <v>28</v>
       </c>
       <c r="F9" s="10">
+        <v>0.19</v>
+      </c>
+      <c r="G9" s="10">
+        <v>-0.44</v>
+      </c>
+      <c r="H9" s="10">
+        <v>0.39600000000000002</v>
+      </c>
+      <c r="K9" s="10">
         <v>0.115</v>
       </c>
-      <c r="G9" s="10">
+      <c r="L9" s="10">
         <v>-0.438</v>
       </c>
-      <c r="H9" s="10">
+      <c r="M9" s="10">
         <v>0.39500000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="8"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9" t="s">
@@ -909,13 +936,22 @@
         <v>0.115</v>
       </c>
       <c r="G10" s="10">
+        <v>0.38</v>
+      </c>
+      <c r="H10" s="10">
+        <v>0.41</v>
+      </c>
+      <c r="K10" s="10">
+        <v>0.115</v>
+      </c>
+      <c r="L10" s="10">
         <v>0.38250000000000001</v>
       </c>
-      <c r="H10" s="10">
+      <c r="M10" s="10">
         <v>0.40200000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9" t="s">
@@ -927,10 +963,10 @@
       <c r="F11" s="10"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
       <c r="B12" s="8" t="s">
         <v>21</v>
@@ -951,7 +987,7 @@
       </c>
       <c r="J12" s="18"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="9" t="s">
@@ -967,11 +1003,20 @@
         <v>0</v>
       </c>
       <c r="H13" s="10">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="J13" s="18"/>
+      <c r="K13" s="10">
+        <v>0</v>
+      </c>
+      <c r="L13" s="10">
+        <v>0</v>
+      </c>
+      <c r="M13" s="10">
         <v>0.38</v>
       </c>
-      <c r="J13" s="18"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
       <c r="B14" s="8" t="s">
         <v>55</v>
@@ -987,7 +1032,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="9" t="s">
@@ -1006,7 +1051,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9" t="s">
@@ -1025,7 +1070,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="9" t="s">
@@ -1040,7 +1085,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="9" t="s">
@@ -1064,7 +1109,7 @@
         <v>-0.04</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="9" t="s">
@@ -1079,7 +1124,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="9" t="s">
@@ -1094,7 +1139,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="9" t="s">
@@ -1109,7 +1154,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
       <c r="B22" s="8" t="s">
         <v>35</v>
@@ -1130,11 +1175,20 @@
         <v>0.63819999999999999</v>
       </c>
       <c r="H22" s="10">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="J22" s="18"/>
+      <c r="K22" s="12">
+        <v>0</v>
+      </c>
+      <c r="L22" s="10">
+        <v>0.63819999999999999</v>
+      </c>
+      <c r="M22" s="10">
         <v>0.38</v>
       </c>
-      <c r="J22" s="18"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="9" t="s">
@@ -1144,13 +1198,13 @@
         <v>8</v>
       </c>
       <c r="F23" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="G23" s="23">
-        <v>0.61470000000000002</v>
+        <v>0.60399999999999998</v>
       </c>
       <c r="H23" s="23">
-        <v>0.45</v>
+        <v>0.37</v>
       </c>
       <c r="J23" s="22" t="s">
         <v>49</v>
@@ -1161,7 +1215,7 @@
       <c r="N23" s="22"/>
       <c r="O23" s="22"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="9" t="s">
@@ -1180,10 +1234,19 @@
         <v>0.74295</v>
       </c>
       <c r="H24" s="10">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="K24" s="10">
+        <v>0</v>
+      </c>
+      <c r="L24" s="10">
+        <v>0.74295</v>
+      </c>
+      <c r="M24" s="10">
         <v>0.38</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="9" t="s">
@@ -1201,7 +1264,7 @@
         <v>-3.25</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="9" t="s">
@@ -1219,7 +1282,7 @@
         <v>7.0110000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="9" t="s">
@@ -1238,7 +1301,7 @@
       </c>
       <c r="J27" s="18"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="8"/>
       <c r="B28" s="8" t="s">
         <v>30</v>
@@ -1253,17 +1316,26 @@
         <v>31</v>
       </c>
       <c r="F28" s="12">
+        <v>-0.17299999999999999</v>
+      </c>
+      <c r="G28" s="10">
+        <v>0.61599999999999999</v>
+      </c>
+      <c r="H28" s="10">
+        <v>0.32600000000000001</v>
+      </c>
+      <c r="J28" s="18"/>
+      <c r="K28" s="12">
         <v>-0.15859999999999999</v>
       </c>
-      <c r="G28" s="10">
+      <c r="L28" s="10">
         <v>0.61470000000000002</v>
       </c>
-      <c r="H28" s="10">
+      <c r="M28" s="10">
         <v>0.30499999999999999</v>
       </c>
-      <c r="J28" s="18"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="8"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9" t="s">
@@ -1278,7 +1350,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="8"/>
       <c r="B30" s="13" t="s">
         <v>11</v>
@@ -1293,13 +1365,13 @@
         <v>24</v>
       </c>
       <c r="F30" s="20">
-        <v>-1.5900000000000001E-2</v>
+        <v>-1.7000000000000001E-2</v>
       </c>
       <c r="G30" s="20">
-        <v>0.50453999999999999</v>
+        <v>0.48399999999999999</v>
       </c>
       <c r="H30" s="20">
-        <v>0.62</v>
+        <v>0.65500000000000003</v>
       </c>
       <c r="J30" s="14" t="s">
         <v>33</v>
@@ -1309,8 +1381,17 @@
       <c r="M30" s="14"/>
       <c r="N30" s="14"/>
       <c r="O30" s="14"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q30" s="20">
+        <v>-1.5900000000000001E-2</v>
+      </c>
+      <c r="R30" s="20">
+        <v>0.50453999999999999</v>
+      </c>
+      <c r="S30" s="20">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="8"/>
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="s">
@@ -1323,13 +1404,13 @@
         <v>23</v>
       </c>
       <c r="F31" s="20">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="G31" s="20">
-        <v>0.50453999999999999</v>
+        <v>0.49</v>
       </c>
       <c r="H31" s="20">
-        <v>0.5</v>
+        <v>0.49199999999999999</v>
       </c>
       <c r="J31" s="14" t="s">
         <v>33</v>
@@ -1339,8 +1420,17 @@
       <c r="M31" s="14"/>
       <c r="N31" s="14"/>
       <c r="O31" s="14"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q31" s="20">
+        <v>0</v>
+      </c>
+      <c r="R31" s="20">
+        <v>0.50453999999999999</v>
+      </c>
+      <c r="S31" s="20">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="9" t="s">

--- a/Libraries/Vehicle/Suspension/AxleTA2PR/sm_car_data_Linkage_AxleTA2PR.xlsx
+++ b/Libraries/Vehicle/Suspension/AxleTA2PR/sm_car_data_Linkage_AxleTA2PR.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SMILLER\TMW\Sharepoint\PM_Evl\sscMbody\2024\2409_VDGUP\Models_and_Files\Proj1\CAD_251201_New\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Suspension\AxleTA2PR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58AFF2DF-F8F5-471A-B616-63199762F47F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8E953BF-8208-4861-A593-B038A51867A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31050" yWindow="2250" windowWidth="21600" windowHeight="11295" tabRatio="794" xr2:uid="{5368FE27-1559-47FB-BDD2-777FB297959A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" activeTab="1" xr2:uid="{5368FE27-1559-47FB-BDD2-777FB297959A}"/>
   </bookViews>
   <sheets>
     <sheet name="AxleTA2PR_SUV_Landy_f" sheetId="5" r:id="rId1"/>
+    <sheet name="AxleTA2PR_Sedan_HambaLG_r" sheetId="6" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="79">
   <si>
     <t>Units</t>
   </si>
@@ -68,18 +69,9 @@
     <t>kg</t>
   </si>
   <si>
-    <t>sWheelCentre</t>
-  </si>
-  <si>
     <t>Shock</t>
   </si>
   <si>
-    <t>sTop</t>
-  </si>
-  <si>
-    <t>sBottom</t>
-  </si>
-  <si>
     <t>mPiston</t>
   </si>
   <si>
@@ -107,21 +99,12 @@
     <t>sAxle</t>
   </si>
   <si>
-    <t>Shock to Axle</t>
-  </si>
-  <si>
-    <t>Shock to Body</t>
-  </si>
-  <si>
     <t>PanhardRod</t>
   </si>
   <si>
     <t>J-01, J-03</t>
   </si>
   <si>
-    <t>J-02, J-04</t>
-  </si>
-  <si>
     <t>J-05</t>
   </si>
   <si>
@@ -131,12 +114,6 @@
     <t>SteeringLink</t>
   </si>
   <si>
-    <t>J-13, J-14</t>
-  </si>
-  <si>
-    <t>J-11, J-12</t>
-  </si>
-  <si>
     <t>Must be consistent with values in Spring, Damper</t>
   </si>
   <si>
@@ -149,9 +126,6 @@
     <t>Upright mass</t>
   </si>
   <si>
-    <t>sOutboard</t>
-  </si>
-  <si>
     <t>Axle housing mass</t>
   </si>
   <si>
@@ -173,21 +147,12 @@
     <t>Kinematic</t>
   </si>
   <si>
-    <t>sDragLink</t>
-  </si>
-  <si>
     <t>CylUpAttCtr</t>
   </si>
   <si>
     <t>Shock Connection</t>
   </si>
   <si>
-    <t>J-15, J-16</t>
-  </si>
-  <si>
-    <t>Must be consistent with values in Steer</t>
-  </si>
-  <si>
     <t>aCaster</t>
   </si>
   <si>
@@ -206,9 +171,6 @@
     <t>Bumpstop</t>
   </si>
   <si>
-    <t>sChassis</t>
-  </si>
-  <si>
     <t>xHeight</t>
   </si>
   <si>
@@ -234,6 +196,84 @@
   </si>
   <si>
     <t>[xyz], npts x 3, ref frame is sChassis</t>
+  </si>
+  <si>
+    <t>sAxleR</t>
+  </si>
+  <si>
+    <t>sAxleL</t>
+  </si>
+  <si>
+    <t>J-02</t>
+  </si>
+  <si>
+    <t>J-04</t>
+  </si>
+  <si>
+    <t>sDragLinkL</t>
+  </si>
+  <si>
+    <t>sDragLinkR</t>
+  </si>
+  <si>
+    <t>sWheelCentreL</t>
+  </si>
+  <si>
+    <t>sWheelCentreR</t>
+  </si>
+  <si>
+    <t>sOutboardL</t>
+  </si>
+  <si>
+    <t>sOutboardR</t>
+  </si>
+  <si>
+    <t>J-14</t>
+  </si>
+  <si>
+    <t>J-13</t>
+  </si>
+  <si>
+    <t>J-16</t>
+  </si>
+  <si>
+    <t>J-15</t>
+  </si>
+  <si>
+    <t>J-12</t>
+  </si>
+  <si>
+    <t>J-11</t>
+  </si>
+  <si>
+    <t>sBottomL</t>
+  </si>
+  <si>
+    <t>sBottomR</t>
+  </si>
+  <si>
+    <t>sTopL</t>
+  </si>
+  <si>
+    <t>sTopR</t>
+  </si>
+  <si>
+    <t>Shock to Body, Right</t>
+  </si>
+  <si>
+    <t>Shock to Body, Left</t>
+  </si>
+  <si>
+    <t>Shock to Axle, Left</t>
+  </si>
+  <si>
+    <t>Shock to Axle, Right</t>
+  </si>
+  <si>
+    <t>Left or Right must be consistent with values in Steer</t>
+  </si>
+  <si>
+    <t>AxleTA2PR_Sedan_HambaLG_r</t>
   </si>
 </sst>
 </file>
@@ -319,7 +359,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -357,18 +397,47 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="8">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -716,7 +785,7 @@
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:S37"/>
+  <dimension ref="A1:S44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="17" customWidth="1"/>
@@ -761,7 +830,7 @@
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -773,7 +842,7 @@
       <c r="F3" s="10"/>
       <c r="G3" s="10"/>
       <c r="H3" s="11" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -787,13 +856,13 @@
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
       <c r="H4" s="7" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="J4" s="18"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>7</v>
@@ -804,757 +873,1880 @@
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="7" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="J5" s="18"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="8"/>
       <c r="B6" s="9" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="10">
-        <v>-0.84</v>
-      </c>
-      <c r="G6" s="10">
-        <v>0.439</v>
-      </c>
-      <c r="H6" s="10">
-        <v>0.39400000000000002</v>
-      </c>
-      <c r="K6" s="10">
-        <v>-0.81950000000000001</v>
-      </c>
-      <c r="L6" s="10">
-        <v>0.438</v>
-      </c>
-      <c r="M6" s="10">
-        <v>0.39500000000000002</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="F6" s="18">
+        <v>-0.83199999999999996</v>
+      </c>
+      <c r="G6" s="18">
+        <v>0.44</v>
+      </c>
+      <c r="H6" s="18">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="8"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
         <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="10">
+        <v>55</v>
+      </c>
+      <c r="F7" s="18">
         <v>0</v>
       </c>
-      <c r="G7" s="10">
-        <v>0.438</v>
-      </c>
-      <c r="H7" s="10">
-        <v>0.38800000000000001</v>
-      </c>
-      <c r="K7" s="10">
-        <v>0</v>
-      </c>
-      <c r="L7" s="10">
-        <v>0.4405</v>
-      </c>
-      <c r="M7" s="10">
-        <v>0.38</v>
-      </c>
+      <c r="G7" s="18">
+        <v>0.44</v>
+      </c>
+      <c r="H7" s="18">
+        <v>0.40300000000000002</v>
+      </c>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9" t="s">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10">
-        <v>10</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="18">
+        <v>0</v>
+      </c>
+      <c r="G8" s="18">
+        <v>-0.435</v>
+      </c>
+      <c r="H8" s="18">
+        <v>0.40300000000000002</v>
+      </c>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
-      <c r="B9" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="B9" s="9"/>
       <c r="C9" s="9" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="10">
-        <v>0.19</v>
-      </c>
-      <c r="G9" s="10">
-        <v>-0.44</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
       <c r="H9" s="10">
-        <v>0.39600000000000002</v>
-      </c>
-      <c r="K9" s="10">
-        <v>0.115</v>
-      </c>
-      <c r="L9" s="10">
-        <v>-0.438</v>
-      </c>
-      <c r="M9" s="10">
-        <v>0.39500000000000002</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="8"/>
-      <c r="B10" s="9"/>
+      <c r="B10" s="9" t="s">
+        <v>20</v>
+      </c>
       <c r="C10" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s">
         <v>22</v>
       </c>
-      <c r="D10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="10">
-        <v>0.115</v>
-      </c>
-      <c r="G10" s="10">
-        <v>0.38</v>
-      </c>
-      <c r="H10" s="10">
-        <v>0.41</v>
-      </c>
-      <c r="K10" s="10">
-        <v>0.115</v>
-      </c>
-      <c r="L10" s="10">
-        <v>0.38250000000000001</v>
-      </c>
-      <c r="M10" s="10">
-        <v>0.40200000000000002</v>
-      </c>
+      <c r="F10" s="18">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="G10" s="18">
+        <v>-0.434</v>
+      </c>
+      <c r="H10" s="18">
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10">
-        <v>4</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="18">
+        <v>0.121</v>
+      </c>
+      <c r="G11" s="18">
+        <v>0.38</v>
+      </c>
+      <c r="H11" s="18">
+        <v>0.41699999999999998</v>
+      </c>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
-      <c r="B12" s="8" t="s">
-        <v>21</v>
-      </c>
+      <c r="B12" s="9"/>
       <c r="C12" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D12" t="s">
         <v>9</v>
       </c>
-      <c r="E12" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="12"/>
+      <c r="F12" s="10"/>
       <c r="G12" s="10"/>
       <c r="H12" s="10">
-        <v>143</v>
-      </c>
-      <c r="J12" s="18"/>
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
+      <c r="B13" s="8" t="s">
+        <v>18</v>
+      </c>
       <c r="C13" s="9" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="10">
-        <v>0</v>
-      </c>
-      <c r="G13" s="10">
-        <v>0</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="E13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="12"/>
+      <c r="G13" s="10"/>
       <c r="H13" s="10">
-        <v>0.38800000000000001</v>
+        <v>143</v>
       </c>
       <c r="J13" s="18"/>
-      <c r="K13" s="10">
-        <v>0</v>
-      </c>
-      <c r="L13" s="10">
-        <v>0</v>
-      </c>
-      <c r="M13" s="10">
-        <v>0.38</v>
-      </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
-      <c r="B14" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="21" t="s">
-        <v>64</v>
-      </c>
+      <c r="B14" s="8"/>
+      <c r="C14" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="10">
+        <v>0</v>
+      </c>
+      <c r="G14" s="10">
+        <v>0</v>
+      </c>
+      <c r="H14" s="10">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="J14" s="18"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="10">
-        <v>0</v>
-      </c>
-      <c r="G15" s="10">
-        <v>0</v>
-      </c>
-      <c r="H15" s="10">
-        <v>0.45</v>
+      <c r="B15" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="19" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="18">
         <v>0</v>
       </c>
-      <c r="G16" s="10">
-        <v>0.35499999999999998</v>
-      </c>
-      <c r="H16" s="10">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="G16" s="18">
+        <v>0</v>
+      </c>
+      <c r="H16" s="18">
+        <v>0.47899999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="9" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="D17" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="F17" s="18">
+        <v>0</v>
+      </c>
+      <c r="G17" s="18">
+        <v>0.35499999999999998</v>
+      </c>
+      <c r="H17" s="18">
+        <v>0.61799999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="9" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="D18" t="s">
         <v>8</v>
-      </c>
-      <c r="E18" t="s">
-        <v>65</v>
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
       <c r="H18" s="10">
-        <v>0</v>
-      </c>
-      <c r="I18" s="10">
-        <v>0</v>
-      </c>
-      <c r="J18" s="10">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="9" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>58</v>
+        <v>8</v>
+      </c>
+      <c r="E19" t="s">
+        <v>52</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="10"/>
       <c r="H19" s="10">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="I19" s="10">
+        <v>0</v>
+      </c>
+      <c r="J19" s="10">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="9" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
       <c r="H20" s="10">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="9" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="D21" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
       <c r="H21" s="10">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10">
         <v>1E-4</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" t="s">
-        <v>32</v>
-      </c>
-      <c r="F22" s="12">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" t="s">
+        <v>68</v>
+      </c>
+      <c r="F23" s="18">
         <v>0</v>
       </c>
-      <c r="G22" s="10">
-        <v>0.63819999999999999</v>
-      </c>
-      <c r="H22" s="10">
-        <v>0.38800000000000001</v>
-      </c>
-      <c r="J22" s="18"/>
-      <c r="K22" s="12">
-        <v>0</v>
-      </c>
-      <c r="L22" s="10">
-        <v>0.63819999999999999</v>
-      </c>
-      <c r="M22" s="10">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" s="23">
-        <v>0.20200000000000001</v>
-      </c>
-      <c r="G23" s="23">
-        <v>0.60399999999999998</v>
-      </c>
-      <c r="H23" s="23">
-        <v>0.37</v>
-      </c>
-      <c r="J23" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="22"/>
-      <c r="N23" s="22"/>
-      <c r="O23" s="22"/>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="G23" s="18">
+        <v>0.64100000000000001</v>
+      </c>
+      <c r="H23" s="18">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="J23" s="18"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="9" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="D24" t="s">
         <v>8</v>
       </c>
       <c r="E24" t="s">
-        <v>48</v>
-      </c>
-      <c r="F24" s="10">
+        <v>67</v>
+      </c>
+      <c r="F24" s="18">
         <v>0</v>
       </c>
-      <c r="G24" s="10">
-        <v>0.74295</v>
-      </c>
-      <c r="H24" s="10">
-        <v>0.38800000000000001</v>
-      </c>
-      <c r="K24" s="10">
-        <v>0</v>
-      </c>
-      <c r="L24" s="10">
-        <v>0.74295</v>
-      </c>
-      <c r="M24" s="10">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="G24" s="18">
+        <v>-0.63600000000000001</v>
+      </c>
+      <c r="H24" s="18">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="J24" s="18"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="9" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D25" t="s">
-        <v>52</v>
-      </c>
-      <c r="E25" t="s">
-        <v>54</v>
-      </c>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10">
-        <v>-3.25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="F25" s="21">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="G25" s="21">
+        <v>0.61</v>
+      </c>
+      <c r="H25" s="21">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="9" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D26" t="s">
-        <v>52</v>
-      </c>
-      <c r="E26" t="s">
-        <v>53</v>
-      </c>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10">
-        <v>7.0110000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="F26" s="21">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="G26" s="21">
+        <v>-0.61</v>
+      </c>
+      <c r="H26" s="21">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="J26" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="9" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E27" t="s">
-        <v>36</v>
-      </c>
-      <c r="F27" s="12"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10">
-        <v>10</v>
-      </c>
-      <c r="J27" s="18"/>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="F27" s="18">
+        <v>0</v>
+      </c>
+      <c r="G27" s="18">
+        <v>0.75900000000000001</v>
+      </c>
+      <c r="H27" s="18">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="8"/>
-      <c r="B28" s="8" t="s">
-        <v>30</v>
-      </c>
+      <c r="B28" s="8"/>
       <c r="C28" s="9" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="D28" t="s">
         <v>8</v>
       </c>
       <c r="E28" t="s">
-        <v>31</v>
-      </c>
-      <c r="F28" s="12">
-        <v>-0.17299999999999999</v>
-      </c>
-      <c r="G28" s="10">
-        <v>0.61599999999999999</v>
-      </c>
-      <c r="H28" s="10">
-        <v>0.32600000000000001</v>
-      </c>
-      <c r="J28" s="18"/>
-      <c r="K28" s="12">
-        <v>-0.15859999999999999</v>
-      </c>
-      <c r="L28" s="10">
-        <v>0.61470000000000002</v>
-      </c>
-      <c r="M28" s="10">
-        <v>0.30499999999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+      <c r="F28" s="18">
+        <v>0</v>
+      </c>
+      <c r="G28" s="18">
+        <v>-0.754</v>
+      </c>
+      <c r="H28" s="18">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="8"/>
-      <c r="B29" s="9"/>
+      <c r="B29" s="8"/>
       <c r="C29" s="9" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="D29" t="s">
-        <v>9</v>
+        <v>40</v>
+      </c>
+      <c r="E29" t="s">
+        <v>42</v>
       </c>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
       <c r="H29" s="10">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-3.25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="8"/>
-      <c r="B30" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>12</v>
+      <c r="B30" s="8"/>
+      <c r="C30" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="D30" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="E30" t="s">
+        <v>41</v>
+      </c>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10">
+        <v>7.0110000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" t="s">
+        <v>28</v>
+      </c>
+      <c r="F31" s="12"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10">
+        <v>10</v>
+      </c>
+      <c r="J31" s="18"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" s="8"/>
+      <c r="B32" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="F30" s="20">
-        <v>-1.7000000000000001E-2</v>
-      </c>
-      <c r="G30" s="20">
-        <v>0.48399999999999999</v>
-      </c>
-      <c r="H30" s="20">
-        <v>0.65500000000000003</v>
-      </c>
-      <c r="J30" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="K30" s="14"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="14"/>
-      <c r="O30" s="14"/>
-      <c r="Q30" s="20">
-        <v>-1.5900000000000001E-2</v>
-      </c>
-      <c r="R30" s="20">
-        <v>0.50453999999999999</v>
-      </c>
-      <c r="S30" s="20">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A31" s="8"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D31" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" t="s">
-        <v>23</v>
-      </c>
-      <c r="F31" s="20">
-        <v>-0.02</v>
-      </c>
-      <c r="G31" s="20">
-        <v>0.49</v>
-      </c>
-      <c r="H31" s="20">
-        <v>0.49199999999999999</v>
-      </c>
-      <c r="J31" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
-      <c r="M31" s="14"/>
-      <c r="N31" s="14"/>
-      <c r="O31" s="14"/>
-      <c r="Q31" s="20">
-        <v>0</v>
-      </c>
-      <c r="R31" s="20">
-        <v>0.50453999999999999</v>
-      </c>
-      <c r="S31" s="20">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
       <c r="C32" s="9" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="D32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10">
-        <v>3.6529410000000002</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="E32" t="s">
+        <v>64</v>
+      </c>
+      <c r="F32" s="18">
+        <v>-0.17299999999999999</v>
+      </c>
+      <c r="G32" s="18">
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="H32" s="18">
+        <v>0.34</v>
+      </c>
+      <c r="J32" s="18"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="10"/>
+      <c r="M32" s="10"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" t="s">
+        <v>63</v>
+      </c>
+      <c r="F33" s="18">
+        <v>-0.17299999999999999</v>
+      </c>
+      <c r="G33" s="18">
+        <v>-0.61199999999999999</v>
+      </c>
+      <c r="H33" s="18">
+        <v>0.34</v>
+      </c>
+      <c r="J33" s="18"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="10"/>
+      <c r="M33" s="10"/>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A34" s="8"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A35" s="8"/>
+      <c r="B35" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D35" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" t="s">
+        <v>74</v>
+      </c>
+      <c r="F35" s="22">
+        <v>-1E-3</v>
+      </c>
+      <c r="G35" s="22">
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="H35" s="22">
+        <v>0.73299999999999998</v>
+      </c>
+      <c r="J35" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
+      <c r="M35" s="14"/>
+      <c r="N35" s="14"/>
+      <c r="O35" s="14"/>
+      <c r="Q35" s="23"/>
+      <c r="R35" s="23"/>
+      <c r="S35" s="23"/>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A36" s="8"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" t="s">
+        <v>73</v>
+      </c>
+      <c r="F36" s="22">
+        <v>-1E-3</v>
+      </c>
+      <c r="G36" s="22">
+        <v>-0.47799999999999998</v>
+      </c>
+      <c r="H36" s="22">
+        <v>0.73299999999999998</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="14"/>
+      <c r="N36" s="14"/>
+      <c r="O36" s="14"/>
+      <c r="Q36" s="23"/>
+      <c r="R36" s="23"/>
+      <c r="S36" s="23"/>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A37" s="8"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D37" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" t="s">
+        <v>75</v>
+      </c>
+      <c r="F37" s="22">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="G37" s="22">
+        <v>0.49299999999999999</v>
+      </c>
+      <c r="H37" s="22">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="J37" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K37" s="14"/>
+      <c r="L37" s="14"/>
+      <c r="M37" s="14"/>
+      <c r="N37" s="14"/>
+      <c r="O37" s="14"/>
+      <c r="Q37" s="23"/>
+      <c r="R37" s="23"/>
+      <c r="S37" s="23"/>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A38" s="8"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D38" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" t="s">
+        <v>76</v>
+      </c>
+      <c r="F38" s="22">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="G38" s="22">
+        <v>-0.48699999999999999</v>
+      </c>
+      <c r="H38" s="22">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="J38" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K38" s="14"/>
+      <c r="L38" s="14"/>
+      <c r="M38" s="14"/>
+      <c r="N38" s="14"/>
+      <c r="O38" s="14"/>
+      <c r="Q38" s="23"/>
+      <c r="R38" s="23"/>
+      <c r="S38" s="23"/>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A39" s="8"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10">
+        <v>3.6529410000000002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="10">
+        <v>4.3157700000000006</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A41" s="8"/>
+      <c r="B41" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="24">
+        <f>0.25+H42</f>
+        <v>0.10500000000000001</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A42" s="8"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="16" t="s">
         <v>15</v>
       </c>
+      <c r="D42" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="24">
+        <v>-0.14499999999999999</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K42" s="5"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A43" s="8"/>
+      <c r="B43" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A44" s="8"/>
+      <c r="B44" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B21">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:C38 C39:C42 B39:B44">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E35:E42">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J41:J42">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8765C0C4-4E7C-43AE-AF6A-012A1CA21E06}">
+  <sheetPr>
+    <tabColor theme="7" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:S44"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" style="17" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="35" customWidth="1"/>
+    <col min="6" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8" customWidth="1"/>
+    <col min="11" max="13" width="6.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="18"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="18"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="8"/>
+      <c r="B6" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="18">
+        <v>0.83199999999999996</v>
+      </c>
+      <c r="G6" s="18">
+        <v>0.44</v>
+      </c>
+      <c r="H6" s="18">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="8"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" s="18">
+        <v>0</v>
+      </c>
+      <c r="G7" s="18">
+        <v>0.44</v>
+      </c>
+      <c r="H7" s="18">
+        <v>0.40300000000000002</v>
+      </c>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="8"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="18">
+        <v>0</v>
+      </c>
+      <c r="G8" s="18">
+        <v>-0.435</v>
+      </c>
+      <c r="H8" s="18">
+        <v>0.40300000000000002</v>
+      </c>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="8"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="18">
+        <v>-0.20699999999999999</v>
+      </c>
+      <c r="G10" s="18">
+        <v>-0.434</v>
+      </c>
+      <c r="H10" s="18">
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="8"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="18">
+        <v>-0.121</v>
+      </c>
+      <c r="G11" s="18">
+        <v>0.38</v>
+      </c>
+      <c r="H11" s="18">
+        <v>0.41699999999999998</v>
+      </c>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="8"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="12"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10">
+        <v>143</v>
+      </c>
+      <c r="J13" s="18"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="10">
+        <v>0</v>
+      </c>
+      <c r="G14" s="10">
+        <v>0</v>
+      </c>
+      <c r="H14" s="10">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="J14" s="18"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="18">
+        <v>0</v>
+      </c>
+      <c r="G16" s="18">
+        <v>0</v>
+      </c>
+      <c r="H16" s="18">
+        <v>0.47899999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="18">
+        <v>0</v>
+      </c>
+      <c r="G17" s="18">
+        <v>0.35499999999999998</v>
+      </c>
+      <c r="H17" s="18">
+        <v>0.61799999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" t="s">
+        <v>52</v>
+      </c>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10">
+        <v>0</v>
+      </c>
+      <c r="I19" s="10">
+        <v>0</v>
+      </c>
+      <c r="J19" s="10">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" t="s">
+        <v>68</v>
+      </c>
+      <c r="F23" s="18">
+        <v>0</v>
+      </c>
+      <c r="G23" s="18">
+        <v>0.64100000000000001</v>
+      </c>
+      <c r="H23" s="18">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="J23" s="18"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="18">
+        <v>0</v>
+      </c>
+      <c r="G24" s="18">
+        <v>-0.63600000000000001</v>
+      </c>
+      <c r="H24" s="18">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="J24" s="18"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="21">
+        <v>-0.126</v>
+      </c>
+      <c r="G25" s="21">
+        <v>0.61299999999999999</v>
+      </c>
+      <c r="H25" s="21">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="21">
+        <v>-0.126</v>
+      </c>
+      <c r="G26" s="21">
+        <v>-0.61299999999999999</v>
+      </c>
+      <c r="H26" s="21">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="J26" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" t="s">
+        <v>66</v>
+      </c>
+      <c r="F27" s="18">
+        <v>0</v>
+      </c>
+      <c r="G27" s="18">
+        <v>0.75900000000000001</v>
+      </c>
+      <c r="H27" s="18">
+        <v>0.36214000000000002</v>
+      </c>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" t="s">
+        <v>65</v>
+      </c>
+      <c r="F28" s="18">
+        <v>0</v>
+      </c>
+      <c r="G28" s="18">
+        <v>-0.754</v>
+      </c>
+      <c r="H28" s="18">
+        <v>0.36214000000000002</v>
+      </c>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" t="s">
+        <v>40</v>
+      </c>
+      <c r="E29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10">
+        <v>-3.25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" t="s">
+        <v>41</v>
+      </c>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10">
+        <v>7.0110000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" t="s">
+        <v>28</v>
+      </c>
+      <c r="F31" s="12"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10">
+        <v>10</v>
+      </c>
+      <c r="J31" s="18"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" s="8"/>
+      <c r="B32" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D32" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" t="s">
+        <v>64</v>
+      </c>
+      <c r="F32" s="18">
+        <v>0.17299999999999999</v>
+      </c>
+      <c r="G32" s="18">
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="H32" s="18">
+        <v>0.34</v>
+      </c>
+      <c r="J32" s="18"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="10"/>
+      <c r="M32" s="10"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="9" t="s">
+        <v>62</v>
+      </c>
       <c r="D33" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" t="s">
+        <v>63</v>
+      </c>
+      <c r="F33" s="18">
+        <v>0.17299999999999999</v>
+      </c>
+      <c r="G33" s="18">
+        <v>-0.61199999999999999</v>
+      </c>
+      <c r="H33" s="18">
+        <v>0.34</v>
+      </c>
+      <c r="J33" s="18"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="10"/>
+      <c r="M33" s="10"/>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A34" s="8"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" t="s">
         <v>9</v>
       </c>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10">
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A35" s="8"/>
+      <c r="B35" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D35" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" t="s">
+        <v>74</v>
+      </c>
+      <c r="F35" s="22">
+        <v>1E-3</v>
+      </c>
+      <c r="G35" s="22">
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="H35" s="22">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="J35" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
+      <c r="M35" s="14"/>
+      <c r="N35" s="14"/>
+      <c r="O35" s="14"/>
+      <c r="Q35" s="23"/>
+      <c r="R35" s="23"/>
+      <c r="S35" s="23"/>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A36" s="8"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" t="s">
+        <v>73</v>
+      </c>
+      <c r="F36" s="22">
+        <v>1E-3</v>
+      </c>
+      <c r="G36" s="22">
+        <v>-0.47799999999999998</v>
+      </c>
+      <c r="H36" s="22">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="14"/>
+      <c r="N36" s="14"/>
+      <c r="O36" s="14"/>
+      <c r="Q36" s="23"/>
+      <c r="R36" s="23"/>
+      <c r="S36" s="23"/>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A37" s="8"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D37" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" t="s">
+        <v>75</v>
+      </c>
+      <c r="F37" s="22">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="G37" s="22">
+        <v>0.49299999999999999</v>
+      </c>
+      <c r="H37" s="22">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="J37" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K37" s="14"/>
+      <c r="L37" s="14"/>
+      <c r="M37" s="14"/>
+      <c r="N37" s="14"/>
+      <c r="O37" s="14"/>
+      <c r="Q37" s="23"/>
+      <c r="R37" s="23"/>
+      <c r="S37" s="23"/>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A38" s="8"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D38" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" t="s">
+        <v>76</v>
+      </c>
+      <c r="F38" s="22">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="G38" s="22">
+        <v>-0.48699999999999999</v>
+      </c>
+      <c r="H38" s="22">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="J38" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K38" s="14"/>
+      <c r="L38" s="14"/>
+      <c r="M38" s="14"/>
+      <c r="N38" s="14"/>
+      <c r="O38" s="14"/>
+      <c r="Q38" s="23"/>
+      <c r="R38" s="23"/>
+      <c r="S38" s="23"/>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A39" s="8"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10">
+        <v>3.6529410000000002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="10">
         <v>4.3157700000000006</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="8"/>
-      <c r="B34" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="D34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="19">
-        <v>0.13500000000000001</v>
-      </c>
-      <c r="J34" s="5" t="s">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A41" s="8"/>
+      <c r="B41" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="24">
+        <v>0.06</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A42" s="8"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="24">
+        <v>-0.08</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K42" s="5"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A43" s="8"/>
+      <c r="B43" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="K34" s="5"/>
-      <c r="L34" s="5"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="8"/>
-      <c r="B35" s="15"/>
-      <c r="C35" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="D35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="19">
-        <v>-0.115</v>
-      </c>
-      <c r="J35" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K35" s="5"/>
-      <c r="L35" s="5"/>
-      <c r="M35" s="5"/>
-      <c r="N35" s="5"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C36" s="4" t="s">
+      <c r="C43" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="21" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C37" s="4" t="s">
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A44" s="8"/>
+      <c r="B44" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="21" t="s">
-        <v>46</v>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="19" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B20">
+  <conditionalFormatting sqref="B21">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C30:C35 B30:B37">
+  <conditionalFormatting sqref="B35:C38 C39:C42 B39:B44">
     <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E30:E35">
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
+  <conditionalFormatting sqref="E35:E42">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J34:J35">
+  <conditionalFormatting sqref="J41:J42">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>

--- a/Libraries/Vehicle/Suspension/AxleTA2PR/sm_car_data_Linkage_AxleTA2PR.xlsx
+++ b/Libraries/Vehicle/Suspension/AxleTA2PR/sm_car_data_Linkage_AxleTA2PR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Suspension\AxleTA2PR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8E953BF-8208-4861-A593-B038A51867A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF561CD-F510-4F2C-A641-5D65D440FF29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" activeTab="1" xr2:uid="{5368FE27-1559-47FB-BDD2-777FB297959A}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{5368FE27-1559-47FB-BDD2-777FB297959A}"/>
   </bookViews>
   <sheets>
     <sheet name="AxleTA2PR_SUV_Landy_f" sheetId="5" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="83">
   <si>
     <t>Units</t>
   </si>
@@ -274,6 +274,18 @@
   </si>
   <si>
     <t>AxleTA2PR_Sedan_HambaLG_r</t>
+  </si>
+  <si>
+    <t>Abstract model of arm bushing stiffness</t>
+  </si>
+  <si>
+    <t>Abstract model of arm bushing damping</t>
+  </si>
+  <si>
+    <t>N*m/deg</t>
+  </si>
+  <si>
+    <t>N*m/(deg/s)</t>
   </si>
 </sst>
 </file>
@@ -409,7 +421,21 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="10">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -785,7 +811,7 @@
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:S44"/>
+  <dimension ref="A1:S46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="17" customWidth="1"/>
@@ -1082,512 +1108,482 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
-      <c r="B15" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="19" t="s">
-        <v>51</v>
+      <c r="B15" s="8"/>
+      <c r="C15" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E15" t="s">
+        <v>79</v>
+      </c>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="D16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="18">
-        <v>0</v>
-      </c>
-      <c r="G16" s="18">
-        <v>0</v>
-      </c>
-      <c r="H16" s="18">
-        <v>0.47899999999999998</v>
+        <v>82</v>
+      </c>
+      <c r="E16" t="s">
+        <v>80</v>
+      </c>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="18">
-        <v>0</v>
-      </c>
-      <c r="G17" s="18">
-        <v>0.35499999999999998</v>
-      </c>
-      <c r="H17" s="18">
-        <v>0.61799999999999999</v>
+      <c r="B17" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="19" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="9" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s">
         <v>8</v>
       </c>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10">
-        <v>0.04</v>
+      <c r="F18" s="18">
+        <v>0</v>
+      </c>
+      <c r="G18" s="18">
+        <v>0</v>
+      </c>
+      <c r="H18" s="18">
+        <v>0.47899999999999998</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="9" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="D19" t="s">
         <v>8</v>
       </c>
-      <c r="E19" t="s">
-        <v>52</v>
-      </c>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10">
-        <v>0</v>
-      </c>
-      <c r="I19" s="10">
-        <v>0</v>
-      </c>
-      <c r="J19" s="10">
-        <v>-0.04</v>
+      <c r="F19" s="18">
+        <v>0</v>
+      </c>
+      <c r="G19" s="18">
+        <v>0.35499999999999998</v>
+      </c>
+      <c r="H19" s="18">
+        <v>0.61799999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="9" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
       <c r="H20" s="10">
-        <v>100000</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="9" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D21" t="s">
-        <v>47</v>
+        <v>8</v>
+      </c>
+      <c r="E21" t="s">
+        <v>52</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
       <c r="H21" s="10">
-        <v>150</v>
+        <v>0</v>
+      </c>
+      <c r="I21" s="10">
+        <v>0</v>
+      </c>
+      <c r="J21" s="10">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D22" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
       <c r="H22" s="10">
-        <v>1E-4</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="8"/>
-      <c r="B23" s="8" t="s">
-        <v>27</v>
-      </c>
+      <c r="B23" s="8"/>
       <c r="C23" s="9" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D23" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" t="s">
-        <v>68</v>
-      </c>
-      <c r="F23" s="18">
-        <v>0</v>
-      </c>
-      <c r="G23" s="18">
-        <v>0.64100000000000001</v>
-      </c>
-      <c r="H23" s="18">
-        <v>0.39900000000000002</v>
-      </c>
-      <c r="J23" s="18"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
+        <v>47</v>
+      </c>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10">
+        <v>150</v>
+      </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D24" t="s">
         <v>8</v>
       </c>
-      <c r="E24" t="s">
-        <v>67</v>
-      </c>
-      <c r="F24" s="18">
-        <v>0</v>
-      </c>
-      <c r="G24" s="18">
-        <v>-0.63600000000000001</v>
-      </c>
-      <c r="H24" s="18">
-        <v>0.39900000000000002</v>
-      </c>
-      <c r="J24" s="18"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10">
+        <v>1E-4</v>
+      </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
+      <c r="B25" s="8" t="s">
+        <v>27</v>
+      </c>
       <c r="C25" s="9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D25" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="21">
-        <v>0.20699999999999999</v>
-      </c>
-      <c r="G25" s="21">
-        <v>0.61</v>
-      </c>
-      <c r="H25" s="21">
-        <v>0.39100000000000001</v>
-      </c>
-      <c r="J25" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20"/>
+      <c r="E25" t="s">
+        <v>68</v>
+      </c>
+      <c r="F25" s="18">
+        <v>0</v>
+      </c>
+      <c r="G25" s="18">
+        <v>0.64100000000000001</v>
+      </c>
+      <c r="H25" s="18">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="J25" s="18"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="9" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D26" t="s">
         <v>8</v>
       </c>
-      <c r="F26" s="21">
-        <v>0.20699999999999999</v>
-      </c>
-      <c r="G26" s="21">
-        <v>-0.61</v>
-      </c>
-      <c r="H26" s="21">
-        <v>0.39100000000000001</v>
-      </c>
-      <c r="J26" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
-      <c r="M26" s="20"/>
-      <c r="N26" s="20"/>
-      <c r="O26" s="20"/>
+      <c r="E26" t="s">
+        <v>67</v>
+      </c>
+      <c r="F26" s="18">
+        <v>0</v>
+      </c>
+      <c r="G26" s="18">
+        <v>-0.63600000000000001</v>
+      </c>
+      <c r="H26" s="18">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="J26" s="18"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D27" t="s">
         <v>8</v>
       </c>
-      <c r="E27" t="s">
-        <v>66</v>
-      </c>
-      <c r="F27" s="18">
-        <v>0</v>
-      </c>
-      <c r="G27" s="18">
-        <v>0.75900000000000001</v>
-      </c>
-      <c r="H27" s="18">
-        <v>0.39900000000000002</v>
-      </c>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
+      <c r="F27" s="21">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="G27" s="21">
+        <v>0.61</v>
+      </c>
+      <c r="H27" s="21">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="J27" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D28" t="s">
         <v>8</v>
       </c>
-      <c r="E28" t="s">
-        <v>65</v>
-      </c>
-      <c r="F28" s="18">
-        <v>0</v>
-      </c>
-      <c r="G28" s="18">
-        <v>-0.754</v>
-      </c>
-      <c r="H28" s="18">
-        <v>0.39900000000000002</v>
-      </c>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
-      <c r="M28" s="10"/>
+      <c r="F28" s="21">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="G28" s="21">
+        <v>-0.61</v>
+      </c>
+      <c r="H28" s="21">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="J28" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="9" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="D29" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E29" t="s">
-        <v>42</v>
-      </c>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10">
-        <v>-3.25</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="F29" s="18">
+        <v>0</v>
+      </c>
+      <c r="G29" s="18">
+        <v>0.75900000000000001</v>
+      </c>
+      <c r="H29" s="18">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="9" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="D30" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E30" t="s">
-        <v>41</v>
-      </c>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10">
-        <v>7.0110000000000001</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="F30" s="18">
+        <v>0</v>
+      </c>
+      <c r="G30" s="18">
+        <v>-0.754</v>
+      </c>
+      <c r="H30" s="18">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="9" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="D31" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="E31" t="s">
-        <v>28</v>
-      </c>
-      <c r="F31" s="12"/>
+        <v>42</v>
+      </c>
+      <c r="F31" s="10"/>
       <c r="G31" s="10"/>
       <c r="H31" s="10">
-        <v>10</v>
-      </c>
-      <c r="J31" s="18"/>
+        <v>-3.25</v>
+      </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="8"/>
-      <c r="B32" s="8" t="s">
-        <v>24</v>
-      </c>
+      <c r="B32" s="8"/>
       <c r="C32" s="9" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="D32" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="E32" t="s">
-        <v>64</v>
-      </c>
-      <c r="F32" s="18">
-        <v>-0.17299999999999999</v>
-      </c>
-      <c r="G32" s="18">
-        <v>0.61799999999999999</v>
-      </c>
-      <c r="H32" s="18">
-        <v>0.34</v>
-      </c>
-      <c r="J32" s="18"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
+        <v>41</v>
+      </c>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10">
+        <v>7.0110000000000001</v>
+      </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="9" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="D33" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E33" t="s">
-        <v>63</v>
-      </c>
-      <c r="F33" s="18">
-        <v>-0.17299999999999999</v>
-      </c>
-      <c r="G33" s="18">
-        <v>-0.61199999999999999</v>
-      </c>
-      <c r="H33" s="18">
-        <v>0.34</v>
+        <v>28</v>
+      </c>
+      <c r="F33" s="12"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10">
+        <v>10</v>
       </c>
       <c r="J33" s="18"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="10"/>
-      <c r="M33" s="10"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="8"/>
-      <c r="B34" s="9"/>
+      <c r="B34" s="8" t="s">
+        <v>24</v>
+      </c>
       <c r="C34" s="9" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="D34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10">
-        <v>0.5</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E34" t="s">
+        <v>64</v>
+      </c>
+      <c r="F34" s="18">
+        <v>-0.17299999999999999</v>
+      </c>
+      <c r="G34" s="18">
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="H34" s="18">
+        <v>0.34</v>
+      </c>
+      <c r="J34" s="18"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="8"/>
-      <c r="B35" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>71</v>
+      <c r="B35" s="8"/>
+      <c r="C35" s="9" t="s">
+        <v>62</v>
       </c>
       <c r="D35" t="s">
         <v>8</v>
       </c>
       <c r="E35" t="s">
-        <v>74</v>
-      </c>
-      <c r="F35" s="22">
-        <v>-1E-3</v>
-      </c>
-      <c r="G35" s="22">
-        <v>0.47799999999999998</v>
-      </c>
-      <c r="H35" s="22">
-        <v>0.73299999999999998</v>
-      </c>
-      <c r="J35" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="K35" s="14"/>
-      <c r="L35" s="14"/>
-      <c r="M35" s="14"/>
-      <c r="N35" s="14"/>
-      <c r="O35" s="14"/>
-      <c r="Q35" s="23"/>
-      <c r="R35" s="23"/>
-      <c r="S35" s="23"/>
+        <v>63</v>
+      </c>
+      <c r="F35" s="18">
+        <v>-0.17299999999999999</v>
+      </c>
+      <c r="G35" s="18">
+        <v>-0.61199999999999999</v>
+      </c>
+      <c r="H35" s="18">
+        <v>0.34</v>
+      </c>
+      <c r="J35" s="18"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" s="8"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="14" t="s">
-        <v>72</v>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9" t="s">
+        <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" t="s">
-        <v>73</v>
-      </c>
-      <c r="F36" s="22">
-        <v>-1E-3</v>
-      </c>
-      <c r="G36" s="22">
-        <v>-0.47799999999999998</v>
-      </c>
-      <c r="H36" s="22">
-        <v>0.73299999999999998</v>
-      </c>
-      <c r="J36" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="K36" s="14"/>
-      <c r="L36" s="14"/>
-      <c r="M36" s="14"/>
-      <c r="N36" s="14"/>
-      <c r="O36" s="14"/>
-      <c r="Q36" s="23"/>
-      <c r="R36" s="23"/>
-      <c r="S36" s="23"/>
+        <v>9</v>
+      </c>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" s="8"/>
-      <c r="B37" s="13"/>
+      <c r="B37" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="C37" s="14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D37" t="s">
         <v>8</v>
       </c>
       <c r="E37" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F37" s="22">
-        <v>-3.0000000000000001E-3</v>
+        <v>-1E-3</v>
       </c>
       <c r="G37" s="22">
-        <v>0.49299999999999999</v>
+        <v>0.47799999999999998</v>
       </c>
       <c r="H37" s="22">
-        <v>0.52300000000000002</v>
+        <v>0.73299999999999998</v>
       </c>
       <c r="J37" s="14" t="s">
         <v>25</v>
@@ -1605,22 +1601,22 @@
       <c r="A38" s="8"/>
       <c r="B38" s="13"/>
       <c r="C38" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D38" t="s">
         <v>8</v>
       </c>
       <c r="E38" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F38" s="22">
-        <v>-3.0000000000000001E-3</v>
+        <v>-1E-3</v>
       </c>
       <c r="G38" s="22">
-        <v>-0.48699999999999999</v>
+        <v>-0.47799999999999998</v>
       </c>
       <c r="H38" s="22">
-        <v>0.52300000000000002</v>
+        <v>0.73299999999999998</v>
       </c>
       <c r="J38" s="14" t="s">
         <v>25</v>
@@ -1636,131 +1632,202 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="9" t="s">
-        <v>11</v>
+      <c r="B39" s="13"/>
+      <c r="C39" s="14" t="s">
+        <v>69</v>
       </c>
       <c r="D39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10">
-        <v>3.6529410000000002</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E39" t="s">
+        <v>75</v>
+      </c>
+      <c r="F39" s="22">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="G39" s="22">
+        <v>0.49299999999999999</v>
+      </c>
+      <c r="H39" s="22">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="J39" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K39" s="14"/>
+      <c r="L39" s="14"/>
+      <c r="M39" s="14"/>
+      <c r="N39" s="14"/>
+      <c r="O39" s="14"/>
+      <c r="Q39" s="23"/>
+      <c r="R39" s="23"/>
+      <c r="S39" s="23"/>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="8"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="9" t="s">
-        <v>12</v>
+      <c r="B40" s="13"/>
+      <c r="C40" s="14" t="s">
+        <v>70</v>
       </c>
       <c r="D40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10">
-        <v>4.3157700000000006</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E40" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40" s="22">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="G40" s="22">
+        <v>-0.48699999999999999</v>
+      </c>
+      <c r="H40" s="22">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="J40" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K40" s="14"/>
+      <c r="L40" s="14"/>
+      <c r="M40" s="14"/>
+      <c r="N40" s="14"/>
+      <c r="O40" s="14"/>
+      <c r="Q40" s="23"/>
+      <c r="R40" s="23"/>
+      <c r="S40" s="23"/>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" s="8"/>
-      <c r="B41" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C41" s="16" t="s">
-        <v>14</v>
+      <c r="B41" s="8"/>
+      <c r="C41" s="9" t="s">
+        <v>11</v>
       </c>
       <c r="D41" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12"/>
-      <c r="H41" s="24">
-        <f>0.25+H42</f>
-        <v>0.10500000000000001</v>
-      </c>
-      <c r="J41" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K41" s="5"/>
-      <c r="L41" s="5"/>
-      <c r="M41" s="5"/>
-      <c r="N41" s="5"/>
+        <v>9</v>
+      </c>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10">
+        <v>3.6529410000000002</v>
+      </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="8"/>
-      <c r="B42" s="15"/>
-      <c r="C42" s="16" t="s">
-        <v>15</v>
+      <c r="B42" s="8"/>
+      <c r="C42" s="9" t="s">
+        <v>12</v>
       </c>
       <c r="D42" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="24">
-        <v>-0.14499999999999999</v>
-      </c>
-      <c r="J42" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K42" s="5"/>
-      <c r="L42" s="5"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="5"/>
+        <v>9</v>
+      </c>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10">
+        <v>4.3157700000000006</v>
+      </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" s="8"/>
-      <c r="B43" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="19" t="s">
-        <v>35</v>
-      </c>
+      <c r="B43" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="24">
+        <f>0.25+H44</f>
+        <v>0.10500000000000001</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="8"/>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="15"/>
+      <c r="C44" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="24">
+        <v>-0.14499999999999999</v>
+      </c>
+      <c r="J44" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A45" s="8"/>
+      <c r="B45" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A46" s="8"/>
+      <c r="B46" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C46" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="19" t="s">
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="19" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B21">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+  <conditionalFormatting sqref="B23">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B35:C38 C39:C42 B39:B44">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+  <conditionalFormatting sqref="B37:C40 C41:C44 B41:B46">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E35:E42">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+  <conditionalFormatting sqref="E37:E44">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J41:J42">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+  <conditionalFormatting sqref="J43:J44">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1773,7 +1840,7 @@
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:S44"/>
+  <dimension ref="A1:S46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="17" customWidth="1"/>
@@ -2070,512 +2137,482 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
-      <c r="B15" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="19" t="s">
-        <v>51</v>
+      <c r="B15" s="8"/>
+      <c r="C15" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E15" t="s">
+        <v>79</v>
+      </c>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="D16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="18">
-        <v>0</v>
-      </c>
-      <c r="G16" s="18">
-        <v>0</v>
-      </c>
-      <c r="H16" s="18">
-        <v>0.47899999999999998</v>
+        <v>82</v>
+      </c>
+      <c r="E16" t="s">
+        <v>80</v>
+      </c>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="18">
-        <v>0</v>
-      </c>
-      <c r="G17" s="18">
-        <v>0.35499999999999998</v>
-      </c>
-      <c r="H17" s="18">
-        <v>0.61799999999999999</v>
+      <c r="B17" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="19" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="9" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s">
         <v>8</v>
       </c>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10">
-        <v>0.04</v>
+      <c r="F18" s="18">
+        <v>0</v>
+      </c>
+      <c r="G18" s="18">
+        <v>0</v>
+      </c>
+      <c r="H18" s="18">
+        <v>0.47899999999999998</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="9" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="D19" t="s">
         <v>8</v>
       </c>
-      <c r="E19" t="s">
-        <v>52</v>
-      </c>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10">
-        <v>0</v>
-      </c>
-      <c r="I19" s="10">
-        <v>0</v>
-      </c>
-      <c r="J19" s="10">
-        <v>-0.04</v>
+      <c r="F19" s="18">
+        <v>0</v>
+      </c>
+      <c r="G19" s="18">
+        <v>0.35499999999999998</v>
+      </c>
+      <c r="H19" s="18">
+        <v>0.61799999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="9" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
       <c r="H20" s="10">
-        <v>100000</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="9" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D21" t="s">
-        <v>47</v>
+        <v>8</v>
+      </c>
+      <c r="E21" t="s">
+        <v>52</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
       <c r="H21" s="10">
-        <v>150</v>
+        <v>0</v>
+      </c>
+      <c r="I21" s="10">
+        <v>0</v>
+      </c>
+      <c r="J21" s="10">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D22" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
       <c r="H22" s="10">
-        <v>1E-4</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="8"/>
-      <c r="B23" s="8" t="s">
-        <v>27</v>
-      </c>
+      <c r="B23" s="8"/>
       <c r="C23" s="9" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D23" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" t="s">
-        <v>68</v>
-      </c>
-      <c r="F23" s="18">
-        <v>0</v>
-      </c>
-      <c r="G23" s="18">
-        <v>0.64100000000000001</v>
-      </c>
-      <c r="H23" s="18">
-        <v>0.39900000000000002</v>
-      </c>
-      <c r="J23" s="18"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
+        <v>47</v>
+      </c>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10">
+        <v>150</v>
+      </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D24" t="s">
         <v>8</v>
       </c>
-      <c r="E24" t="s">
-        <v>67</v>
-      </c>
-      <c r="F24" s="18">
-        <v>0</v>
-      </c>
-      <c r="G24" s="18">
-        <v>-0.63600000000000001</v>
-      </c>
-      <c r="H24" s="18">
-        <v>0.39900000000000002</v>
-      </c>
-      <c r="J24" s="18"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10">
+        <v>1E-4</v>
+      </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
+      <c r="B25" s="8" t="s">
+        <v>27</v>
+      </c>
       <c r="C25" s="9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D25" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="21">
-        <v>-0.126</v>
-      </c>
-      <c r="G25" s="21">
-        <v>0.61299999999999999</v>
-      </c>
-      <c r="H25" s="21">
-        <v>0.26500000000000001</v>
-      </c>
-      <c r="J25" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20"/>
+      <c r="E25" t="s">
+        <v>68</v>
+      </c>
+      <c r="F25" s="18">
+        <v>0</v>
+      </c>
+      <c r="G25" s="18">
+        <v>0.64100000000000001</v>
+      </c>
+      <c r="H25" s="18">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="J25" s="18"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="9" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D26" t="s">
         <v>8</v>
       </c>
-      <c r="F26" s="21">
-        <v>-0.126</v>
-      </c>
-      <c r="G26" s="21">
-        <v>-0.61299999999999999</v>
-      </c>
-      <c r="H26" s="21">
-        <v>0.26500000000000001</v>
-      </c>
-      <c r="J26" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
-      <c r="M26" s="20"/>
-      <c r="N26" s="20"/>
-      <c r="O26" s="20"/>
+      <c r="E26" t="s">
+        <v>67</v>
+      </c>
+      <c r="F26" s="18">
+        <v>0</v>
+      </c>
+      <c r="G26" s="18">
+        <v>-0.63600000000000001</v>
+      </c>
+      <c r="H26" s="18">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="J26" s="18"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D27" t="s">
         <v>8</v>
       </c>
-      <c r="E27" t="s">
-        <v>66</v>
-      </c>
-      <c r="F27" s="18">
-        <v>0</v>
-      </c>
-      <c r="G27" s="18">
-        <v>0.75900000000000001</v>
-      </c>
-      <c r="H27" s="18">
-        <v>0.36214000000000002</v>
-      </c>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
+      <c r="F27" s="21">
+        <v>-0.126</v>
+      </c>
+      <c r="G27" s="21">
+        <v>0.61299999999999999</v>
+      </c>
+      <c r="H27" s="21">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="J27" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D28" t="s">
         <v>8</v>
       </c>
-      <c r="E28" t="s">
-        <v>65</v>
-      </c>
-      <c r="F28" s="18">
-        <v>0</v>
-      </c>
-      <c r="G28" s="18">
-        <v>-0.754</v>
-      </c>
-      <c r="H28" s="18">
-        <v>0.36214000000000002</v>
-      </c>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
-      <c r="M28" s="10"/>
+      <c r="F28" s="21">
+        <v>-0.126</v>
+      </c>
+      <c r="G28" s="21">
+        <v>-0.61299999999999999</v>
+      </c>
+      <c r="H28" s="21">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="J28" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="9" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="D29" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E29" t="s">
-        <v>42</v>
-      </c>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10">
-        <v>-3.25</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="F29" s="18">
+        <v>0</v>
+      </c>
+      <c r="G29" s="18">
+        <v>0.75900000000000001</v>
+      </c>
+      <c r="H29" s="18">
+        <v>0.36214000000000002</v>
+      </c>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="9" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="D30" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E30" t="s">
-        <v>41</v>
-      </c>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10">
-        <v>7.0110000000000001</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="F30" s="18">
+        <v>0</v>
+      </c>
+      <c r="G30" s="18">
+        <v>-0.754</v>
+      </c>
+      <c r="H30" s="18">
+        <v>0.36214000000000002</v>
+      </c>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="9" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="D31" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="E31" t="s">
-        <v>28</v>
-      </c>
-      <c r="F31" s="12"/>
+        <v>42</v>
+      </c>
+      <c r="F31" s="10"/>
       <c r="G31" s="10"/>
       <c r="H31" s="10">
-        <v>10</v>
-      </c>
-      <c r="J31" s="18"/>
+        <v>-3.25</v>
+      </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="8"/>
-      <c r="B32" s="8" t="s">
-        <v>24</v>
-      </c>
+      <c r="B32" s="8"/>
       <c r="C32" s="9" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="D32" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="E32" t="s">
-        <v>64</v>
-      </c>
-      <c r="F32" s="18">
-        <v>0.17299999999999999</v>
-      </c>
-      <c r="G32" s="18">
-        <v>0.61799999999999999</v>
-      </c>
-      <c r="H32" s="18">
-        <v>0.34</v>
-      </c>
-      <c r="J32" s="18"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
+        <v>41</v>
+      </c>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10">
+        <v>7.0110000000000001</v>
+      </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="9" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="D33" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E33" t="s">
-        <v>63</v>
-      </c>
-      <c r="F33" s="18">
-        <v>0.17299999999999999</v>
-      </c>
-      <c r="G33" s="18">
-        <v>-0.61199999999999999</v>
-      </c>
-      <c r="H33" s="18">
-        <v>0.34</v>
+        <v>28</v>
+      </c>
+      <c r="F33" s="12"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10">
+        <v>10</v>
       </c>
       <c r="J33" s="18"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="10"/>
-      <c r="M33" s="10"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="8"/>
-      <c r="B34" s="9"/>
+      <c r="B34" s="8" t="s">
+        <v>24</v>
+      </c>
       <c r="C34" s="9" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="D34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10">
-        <v>0.5</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E34" t="s">
+        <v>64</v>
+      </c>
+      <c r="F34" s="18">
+        <v>0.17299999999999999</v>
+      </c>
+      <c r="G34" s="18">
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="H34" s="18">
+        <v>0.34</v>
+      </c>
+      <c r="J34" s="18"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="8"/>
-      <c r="B35" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>71</v>
+      <c r="B35" s="8"/>
+      <c r="C35" s="9" t="s">
+        <v>62</v>
       </c>
       <c r="D35" t="s">
         <v>8</v>
       </c>
       <c r="E35" t="s">
-        <v>74</v>
-      </c>
-      <c r="F35" s="22">
-        <v>1E-3</v>
-      </c>
-      <c r="G35" s="22">
-        <v>0.47799999999999998</v>
-      </c>
-      <c r="H35" s="22">
-        <v>0.83299999999999996</v>
-      </c>
-      <c r="J35" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="K35" s="14"/>
-      <c r="L35" s="14"/>
-      <c r="M35" s="14"/>
-      <c r="N35" s="14"/>
-      <c r="O35" s="14"/>
-      <c r="Q35" s="23"/>
-      <c r="R35" s="23"/>
-      <c r="S35" s="23"/>
+        <v>63</v>
+      </c>
+      <c r="F35" s="18">
+        <v>0.17299999999999999</v>
+      </c>
+      <c r="G35" s="18">
+        <v>-0.61199999999999999</v>
+      </c>
+      <c r="H35" s="18">
+        <v>0.34</v>
+      </c>
+      <c r="J35" s="18"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" s="8"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="14" t="s">
-        <v>72</v>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9" t="s">
+        <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" t="s">
-        <v>73</v>
-      </c>
-      <c r="F36" s="22">
-        <v>1E-3</v>
-      </c>
-      <c r="G36" s="22">
-        <v>-0.47799999999999998</v>
-      </c>
-      <c r="H36" s="22">
-        <v>0.83299999999999996</v>
-      </c>
-      <c r="J36" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="K36" s="14"/>
-      <c r="L36" s="14"/>
-      <c r="M36" s="14"/>
-      <c r="N36" s="14"/>
-      <c r="O36" s="14"/>
-      <c r="Q36" s="23"/>
-      <c r="R36" s="23"/>
-      <c r="S36" s="23"/>
+        <v>9</v>
+      </c>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" s="8"/>
-      <c r="B37" s="13"/>
+      <c r="B37" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="C37" s="14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D37" t="s">
         <v>8</v>
       </c>
       <c r="E37" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F37" s="22">
-        <v>3.0000000000000001E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="G37" s="22">
-        <v>0.49299999999999999</v>
+        <v>0.47799999999999998</v>
       </c>
       <c r="H37" s="22">
-        <v>0.52300000000000002</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="J37" s="14" t="s">
         <v>25</v>
@@ -2593,22 +2630,22 @@
       <c r="A38" s="8"/>
       <c r="B38" s="13"/>
       <c r="C38" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D38" t="s">
         <v>8</v>
       </c>
       <c r="E38" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F38" s="22">
-        <v>3.0000000000000001E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="G38" s="22">
-        <v>-0.48699999999999999</v>
+        <v>-0.47799999999999998</v>
       </c>
       <c r="H38" s="22">
-        <v>0.52300000000000002</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="J38" s="14" t="s">
         <v>25</v>
@@ -2624,130 +2661,201 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="9" t="s">
-        <v>11</v>
+      <c r="B39" s="13"/>
+      <c r="C39" s="14" t="s">
+        <v>69</v>
       </c>
       <c r="D39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10">
-        <v>3.6529410000000002</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E39" t="s">
+        <v>75</v>
+      </c>
+      <c r="F39" s="22">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="G39" s="22">
+        <v>0.49299999999999999</v>
+      </c>
+      <c r="H39" s="22">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="J39" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K39" s="14"/>
+      <c r="L39" s="14"/>
+      <c r="M39" s="14"/>
+      <c r="N39" s="14"/>
+      <c r="O39" s="14"/>
+      <c r="Q39" s="23"/>
+      <c r="R39" s="23"/>
+      <c r="S39" s="23"/>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="8"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="9" t="s">
-        <v>12</v>
+      <c r="B40" s="13"/>
+      <c r="C40" s="14" t="s">
+        <v>70</v>
       </c>
       <c r="D40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10">
-        <v>4.3157700000000006</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E40" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40" s="22">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="G40" s="22">
+        <v>-0.48699999999999999</v>
+      </c>
+      <c r="H40" s="22">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="J40" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K40" s="14"/>
+      <c r="L40" s="14"/>
+      <c r="M40" s="14"/>
+      <c r="N40" s="14"/>
+      <c r="O40" s="14"/>
+      <c r="Q40" s="23"/>
+      <c r="R40" s="23"/>
+      <c r="S40" s="23"/>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" s="8"/>
-      <c r="B41" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C41" s="16" t="s">
-        <v>14</v>
+      <c r="B41" s="8"/>
+      <c r="C41" s="9" t="s">
+        <v>11</v>
       </c>
       <c r="D41" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12"/>
-      <c r="H41" s="24">
-        <v>0.06</v>
-      </c>
-      <c r="J41" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K41" s="5"/>
-      <c r="L41" s="5"/>
-      <c r="M41" s="5"/>
-      <c r="N41" s="5"/>
+        <v>9</v>
+      </c>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10">
+        <v>3.6529410000000002</v>
+      </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="8"/>
-      <c r="B42" s="15"/>
-      <c r="C42" s="16" t="s">
-        <v>15</v>
+      <c r="B42" s="8"/>
+      <c r="C42" s="9" t="s">
+        <v>12</v>
       </c>
       <c r="D42" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="24">
-        <v>-0.08</v>
-      </c>
-      <c r="J42" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K42" s="5"/>
-      <c r="L42" s="5"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="5"/>
+        <v>9</v>
+      </c>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10">
+        <v>4.3157700000000006</v>
+      </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" s="8"/>
-      <c r="B43" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="19" t="s">
-        <v>35</v>
-      </c>
+      <c r="B43" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="24">
+        <v>0.06</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="8"/>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="15"/>
+      <c r="C44" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="24">
+        <v>-0.08</v>
+      </c>
+      <c r="J44" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A45" s="8"/>
+      <c r="B45" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A46" s="8"/>
+      <c r="B46" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C46" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="19" t="s">
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="19" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B21">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+  <conditionalFormatting sqref="B23">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B35:C38 C39:C42 B39:B44">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+  <conditionalFormatting sqref="B37:C40 C41:C44 B41:B46">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E35:E42">
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+  <conditionalFormatting sqref="E37:E44">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J41:J42">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+  <conditionalFormatting sqref="J43:J44">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
